--- a/tests/fixtures/controls/C23024/package/rebate_Q2_2026.xlsx
+++ b/tests/fixtures/controls/C23024/package/rebate_Q2_2026.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>priya.sharma@hp.com</t>
+          <t>priya.sharma@example.com</t>
         </is>
       </c>
     </row>
